--- a/snapshots/2026-07-27.xlsx
+++ b/snapshots/2026-07-27.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Acer\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{657BA77C-D1D7-48B1-83A8-AC7E45A7CF69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{74E2AA18-46FE-4366-8AA3-7B00C5C60676}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1512" uniqueCount="219">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1512" uniqueCount="217">
   <si>
     <t>Bandipora</t>
   </si>
@@ -684,12 +684,6 @@
   </si>
   <si>
     <t>SUBMITTED</t>
-  </si>
-  <si>
-    <t>Sajad Ahmad Bhat</t>
-  </si>
-  <si>
-    <t>Tufail Ahmad Bhat</t>
   </si>
 </sst>
 </file>
@@ -807,7 +801,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
@@ -856,10 +850,25 @@
     <xf numFmtId="0" fontId="4" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1177,10 +1186,11 @@
   <dimension ref="A1:J125"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
+    <col min="3" max="3" width="21.7109375" customWidth="1"/>
     <col min="4" max="4" width="16.28515625" customWidth="1"/>
     <col min="5" max="5" width="14" customWidth="1"/>
     <col min="6" max="6" width="14.140625" customWidth="1"/>
-    <col min="8" max="8" width="17" style="23" customWidth="1"/>
+    <col min="8" max="8" width="17" style="22" customWidth="1"/>
     <col min="9" max="9" width="13.42578125" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1238,10 +1248,10 @@
       <c r="G2" s="6">
         <v>286</v>
       </c>
-      <c r="H2" s="22" t="s">
+      <c r="H2" s="25" t="s">
         <v>105</v>
       </c>
-      <c r="I2" s="1">
+      <c r="I2" s="26">
         <v>11</v>
       </c>
       <c r="J2" s="3" t="str">
@@ -1271,7 +1281,7 @@
       <c r="G3" s="6">
         <v>739</v>
       </c>
-      <c r="H3" s="22" t="s">
+      <c r="H3" s="24" t="s">
         <v>10</v>
       </c>
       <c r="I3" s="2">
@@ -1304,7 +1314,7 @@
       <c r="G4" s="6">
         <v>1066</v>
       </c>
-      <c r="H4" s="22" t="s">
+      <c r="H4" s="23" t="s">
         <v>11</v>
       </c>
       <c r="I4" s="1">
@@ -1337,11 +1347,11 @@
       <c r="G5" s="6">
         <v>3312</v>
       </c>
-      <c r="H5" s="22" t="s">
+      <c r="H5" s="23" t="s">
         <v>1</v>
       </c>
       <c r="I5" s="1">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="J5" s="3" t="str">
         <f t="shared" si="0"/>
@@ -1370,11 +1380,11 @@
       <c r="G6" s="6">
         <v>6138</v>
       </c>
-      <c r="H6" s="22" t="s">
+      <c r="H6" s="24" t="s">
         <v>4</v>
       </c>
       <c r="I6" s="2">
-        <v>4</v>
+        <v>42</v>
       </c>
       <c r="J6" s="3" t="str">
         <f t="shared" si="0"/>
@@ -1403,7 +1413,7 @@
       <c r="G7" s="6">
         <v>1628</v>
       </c>
-      <c r="H7" s="22" t="s">
+      <c r="H7" s="24" t="s">
         <v>12</v>
       </c>
       <c r="I7" s="2">
@@ -1436,7 +1446,7 @@
       <c r="G8" s="6">
         <v>3909</v>
       </c>
-      <c r="H8" s="22" t="s">
+      <c r="H8" s="23" t="s">
         <v>13</v>
       </c>
       <c r="I8" s="1">
@@ -1469,11 +1479,11 @@
       <c r="G9" s="6">
         <v>3453</v>
       </c>
-      <c r="H9" s="22" t="s">
+      <c r="H9" s="24" t="s">
         <v>84</v>
       </c>
       <c r="I9" s="2">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="J9" s="3" t="str">
         <f t="shared" si="0"/>
@@ -1502,11 +1512,11 @@
       <c r="G10" s="6">
         <v>2204</v>
       </c>
-      <c r="H10" s="22" t="s">
+      <c r="H10" s="23" t="s">
         <v>5</v>
       </c>
       <c r="I10" s="1">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="J10" s="3" t="str">
         <f t="shared" si="0"/>
@@ -1535,7 +1545,7 @@
       <c r="G11" s="6">
         <v>1162</v>
       </c>
-      <c r="H11" s="22" t="s">
+      <c r="H11" s="24" t="s">
         <v>14</v>
       </c>
       <c r="I11" s="2">
@@ -1568,7 +1578,7 @@
       <c r="G12" s="6">
         <v>1336</v>
       </c>
-      <c r="H12" s="22" t="s">
+      <c r="H12" s="23" t="s">
         <v>15</v>
       </c>
       <c r="I12" s="1">
@@ -1601,7 +1611,7 @@
       <c r="G13" s="6">
         <v>737</v>
       </c>
-      <c r="H13" s="22" t="s">
+      <c r="H13" s="24" t="s">
         <v>106</v>
       </c>
       <c r="I13" s="2">
@@ -1634,7 +1644,7 @@
       <c r="G14" s="6">
         <v>1943</v>
       </c>
-      <c r="H14" s="22" t="s">
+      <c r="H14" s="23" t="s">
         <v>52</v>
       </c>
       <c r="I14" s="1">
@@ -1667,7 +1677,7 @@
       <c r="G15" s="6">
         <v>2940</v>
       </c>
-      <c r="H15" s="22" t="s">
+      <c r="H15" s="24" t="s">
         <v>62</v>
       </c>
       <c r="I15" s="2">
@@ -1700,7 +1710,7 @@
       <c r="G16" s="6">
         <v>4783</v>
       </c>
-      <c r="H16" s="22" t="s">
+      <c r="H16" s="24" t="s">
         <v>0</v>
       </c>
       <c r="I16" s="2">
@@ -1733,7 +1743,7 @@
       <c r="G17" s="6">
         <v>429</v>
       </c>
-      <c r="H17" s="22" t="s">
+      <c r="H17" s="23" t="s">
         <v>107</v>
       </c>
       <c r="I17" s="1">
@@ -1766,7 +1776,7 @@
       <c r="G18" s="6">
         <v>570</v>
       </c>
-      <c r="H18" s="22" t="s">
+      <c r="H18" s="23" t="s">
         <v>16</v>
       </c>
       <c r="I18" s="1">
@@ -1799,7 +1809,7 @@
       <c r="G19" s="6">
         <v>5202</v>
       </c>
-      <c r="H19" s="22" t="s">
+      <c r="H19" s="24" t="s">
         <v>17</v>
       </c>
       <c r="I19" s="2">
@@ -1832,7 +1842,7 @@
       <c r="G20" s="6">
         <v>902</v>
       </c>
-      <c r="H20" s="22" t="s">
+      <c r="H20" s="23" t="s">
         <v>18</v>
       </c>
       <c r="I20" s="1">
@@ -1865,7 +1875,7 @@
       <c r="G21" s="6">
         <v>822</v>
       </c>
-      <c r="H21" s="22" t="s">
+      <c r="H21" s="24" t="s">
         <v>108</v>
       </c>
       <c r="I21" s="2">
@@ -1898,7 +1908,7 @@
       <c r="G22" s="6">
         <v>646</v>
       </c>
-      <c r="H22" s="22" t="s">
+      <c r="H22" s="23" t="s">
         <v>109</v>
       </c>
       <c r="I22" s="1">
@@ -1931,7 +1941,7 @@
       <c r="G23" s="6">
         <v>257</v>
       </c>
-      <c r="H23" s="22" t="s">
+      <c r="H23" s="24" t="s">
         <v>19</v>
       </c>
       <c r="I23" s="2">
@@ -1964,7 +1974,7 @@
       <c r="G24" s="6">
         <v>1429</v>
       </c>
-      <c r="H24" s="22" t="s">
+      <c r="H24" s="23" t="s">
         <v>63</v>
       </c>
       <c r="I24" s="1">
@@ -1997,11 +2007,11 @@
       <c r="G25" s="6">
         <v>303</v>
       </c>
-      <c r="H25" s="22" t="s">
+      <c r="H25" s="24" t="s">
         <v>21</v>
       </c>
       <c r="I25" s="2">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="J25" s="3" t="str">
         <f t="shared" si="0"/>
@@ -2030,11 +2040,11 @@
       <c r="G26" s="6">
         <v>525</v>
       </c>
-      <c r="H26" s="22" t="s">
+      <c r="H26" s="23" t="s">
         <v>20</v>
       </c>
       <c r="I26" s="1">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="J26" s="3" t="str">
         <f t="shared" si="0"/>
@@ -2063,11 +2073,11 @@
       <c r="G27" s="12">
         <v>1515</v>
       </c>
-      <c r="H27" s="22" t="s">
+      <c r="H27" s="23" t="s">
         <v>85</v>
       </c>
       <c r="I27" s="1">
-        <v>173</v>
+        <v>204</v>
       </c>
       <c r="J27" s="3" t="str">
         <f t="shared" si="0"/>
@@ -2096,7 +2106,7 @@
       <c r="G28" s="6">
         <v>3473</v>
       </c>
-      <c r="H28" s="22" t="s">
+      <c r="H28" s="23" t="s">
         <v>22</v>
       </c>
       <c r="I28" s="1">
@@ -2129,11 +2139,11 @@
       <c r="G29" s="6">
         <v>1450</v>
       </c>
-      <c r="H29" s="22" t="s">
+      <c r="H29" s="24" t="s">
         <v>23</v>
       </c>
       <c r="I29" s="2">
-        <v>16</v>
+        <v>41</v>
       </c>
       <c r="J29" s="3" t="str">
         <f t="shared" si="0"/>
@@ -2162,11 +2172,11 @@
       <c r="G30" s="6">
         <v>698</v>
       </c>
-      <c r="H30" s="22" t="s">
+      <c r="H30" s="23" t="s">
         <v>24</v>
       </c>
       <c r="I30" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J30" s="3" t="str">
         <f t="shared" si="0"/>
@@ -2195,11 +2205,11 @@
       <c r="G31" s="6">
         <v>1172</v>
       </c>
-      <c r="H31" s="22" t="s">
+      <c r="H31" s="24" t="s">
         <v>53</v>
       </c>
       <c r="I31" s="2">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="J31" s="3" t="str">
         <f t="shared" si="0"/>
@@ -2228,7 +2238,7 @@
       <c r="G32" s="6">
         <v>302</v>
       </c>
-      <c r="H32" s="22" t="s">
+      <c r="H32" s="24" t="s">
         <v>110</v>
       </c>
       <c r="I32" s="2">
@@ -2261,7 +2271,7 @@
       <c r="G33" s="6">
         <v>371</v>
       </c>
-      <c r="H33" s="22" t="s">
+      <c r="H33" s="24" t="s">
         <v>86</v>
       </c>
       <c r="I33" s="2">
@@ -2294,7 +2304,7 @@
       <c r="G34" s="6">
         <v>676</v>
       </c>
-      <c r="H34" s="22" t="s">
+      <c r="H34" s="24" t="s">
         <v>25</v>
       </c>
       <c r="I34" s="2">
@@ -2327,11 +2337,11 @@
       <c r="G35" s="6">
         <v>2131</v>
       </c>
-      <c r="H35" s="22" t="s">
+      <c r="H35" s="23" t="s">
         <v>87</v>
       </c>
       <c r="I35" s="1">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="J35" s="3" t="str">
         <f t="shared" si="0"/>
@@ -2360,11 +2370,11 @@
       <c r="G36" s="6">
         <v>2966</v>
       </c>
-      <c r="H36" s="22" t="s">
+      <c r="H36" s="23" t="s">
         <v>26</v>
       </c>
       <c r="I36" s="1">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="J36" s="3" t="str">
         <f t="shared" si="0"/>
@@ -2393,11 +2403,11 @@
       <c r="G37" s="6">
         <v>1369</v>
       </c>
-      <c r="H37" s="22" t="s">
+      <c r="H37" s="24" t="s">
         <v>88</v>
       </c>
       <c r="I37" s="2">
-        <v>40</v>
+        <v>58</v>
       </c>
       <c r="J37" s="3" t="str">
         <f t="shared" si="0"/>
@@ -2426,7 +2436,7 @@
       <c r="G38" s="6">
         <v>798</v>
       </c>
-      <c r="H38" s="22" t="s">
+      <c r="H38" s="23" t="s">
         <v>111</v>
       </c>
       <c r="I38" s="1">
@@ -2459,11 +2469,11 @@
       <c r="G39" s="6">
         <v>19</v>
       </c>
-      <c r="H39" s="22" t="s">
+      <c r="H39" s="24" t="s">
         <v>64</v>
       </c>
       <c r="I39" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J39" s="3" t="str">
         <f t="shared" si="0"/>
@@ -2492,7 +2502,7 @@
       <c r="G40" s="6">
         <v>1275</v>
       </c>
-      <c r="H40" s="22" t="s">
+      <c r="H40" s="23" t="s">
         <v>54</v>
       </c>
       <c r="I40" s="1">
@@ -2525,11 +2535,11 @@
       <c r="G41" s="6">
         <v>829</v>
       </c>
-      <c r="H41" s="22" t="s">
+      <c r="H41" s="23" t="s">
         <v>54</v>
       </c>
       <c r="I41" s="1">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="J41" s="3" t="str">
         <f t="shared" si="0"/>
@@ -2558,7 +2568,7 @@
       <c r="G42" s="6">
         <v>691</v>
       </c>
-      <c r="H42" s="22" t="s">
+      <c r="H42" s="24" t="s">
         <v>27</v>
       </c>
       <c r="I42" s="2">
@@ -2591,7 +2601,7 @@
       <c r="G43" s="6">
         <v>222</v>
       </c>
-      <c r="H43" s="22" t="s">
+      <c r="H43" s="24" t="s">
         <v>112</v>
       </c>
       <c r="I43" s="2">
@@ -2624,7 +2634,7 @@
       <c r="G44" s="6">
         <v>643</v>
       </c>
-      <c r="H44" s="22" t="s">
+      <c r="H44" s="24" t="s">
         <v>29</v>
       </c>
       <c r="I44" s="2">
@@ -2657,11 +2667,11 @@
       <c r="G45" s="6">
         <v>830</v>
       </c>
-      <c r="H45" s="22" t="s">
+      <c r="H45" s="23" t="s">
         <v>66</v>
       </c>
       <c r="I45" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J45" s="3" t="str">
         <f t="shared" si="0"/>
@@ -2690,7 +2700,7 @@
       <c r="G46" s="6">
         <v>1485</v>
       </c>
-      <c r="H46" s="22" t="s">
+      <c r="H46" s="24" t="s">
         <v>67</v>
       </c>
       <c r="I46" s="2">
@@ -2723,7 +2733,7 @@
       <c r="G47" s="6">
         <v>6</v>
       </c>
-      <c r="H47" s="22" t="s">
+      <c r="H47" s="24" t="s">
         <v>69</v>
       </c>
       <c r="I47" s="2">
@@ -2756,11 +2766,11 @@
       <c r="G48" s="6">
         <v>2909</v>
       </c>
-      <c r="H48" s="22" t="s">
+      <c r="H48" s="23" t="s">
         <v>70</v>
       </c>
       <c r="I48" s="1">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="J48" s="3" t="str">
         <f t="shared" si="0"/>
@@ -2789,11 +2799,11 @@
       <c r="G49" s="6">
         <v>258</v>
       </c>
-      <c r="H49" s="22" t="s">
+      <c r="H49" s="24" t="s">
         <v>65</v>
       </c>
       <c r="I49" s="2">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J49" s="3" t="str">
         <f t="shared" si="0"/>
@@ -2822,11 +2832,11 @@
       <c r="G50" s="6">
         <v>531</v>
       </c>
-      <c r="H50" s="22" t="s">
+      <c r="H50" s="23" t="s">
         <v>89</v>
       </c>
       <c r="I50" s="1">
-        <v>61</v>
+        <v>101</v>
       </c>
       <c r="J50" s="3" t="str">
         <f t="shared" si="0"/>
@@ -2855,7 +2865,7 @@
       <c r="G51" s="6">
         <v>1366</v>
       </c>
-      <c r="H51" s="22" t="s">
+      <c r="H51" s="23" t="s">
         <v>28</v>
       </c>
       <c r="I51" s="1">
@@ -2888,7 +2898,7 @@
       <c r="G52" s="6">
         <v>899</v>
       </c>
-      <c r="H52" s="22" t="s">
+      <c r="H52" s="23" t="s">
         <v>68</v>
       </c>
       <c r="I52" s="1">
@@ -2921,7 +2931,7 @@
       <c r="G53" s="6">
         <v>7372</v>
       </c>
-      <c r="H53" s="22" t="s">
+      <c r="H53" s="24" t="s">
         <v>61</v>
       </c>
       <c r="I53" s="2">
@@ -2954,11 +2964,11 @@
       <c r="G54" s="6">
         <v>2029</v>
       </c>
-      <c r="H54" s="22" t="s">
+      <c r="H54" s="24" t="s">
         <v>90</v>
       </c>
       <c r="I54" s="2">
-        <v>28</v>
+        <v>55</v>
       </c>
       <c r="J54" s="3" t="str">
         <f t="shared" si="0"/>
@@ -2987,7 +2997,7 @@
       <c r="G55" s="6">
         <v>362</v>
       </c>
-      <c r="H55" s="22" t="s">
+      <c r="H55" s="23" t="s">
         <v>113</v>
       </c>
       <c r="I55" s="1">
@@ -3020,7 +3030,7 @@
       <c r="G56" s="6">
         <v>769</v>
       </c>
-      <c r="H56" s="22" t="s">
+      <c r="H56" s="24" t="s">
         <v>114</v>
       </c>
       <c r="I56" s="2">
@@ -3053,7 +3063,7 @@
       <c r="G57" s="6">
         <v>4570</v>
       </c>
-      <c r="H57" s="22" t="s">
+      <c r="H57" s="23" t="s">
         <v>30</v>
       </c>
       <c r="I57" s="1">
@@ -3086,7 +3096,7 @@
       <c r="G58" s="6">
         <v>325</v>
       </c>
-      <c r="H58" s="22" t="s">
+      <c r="H58" s="23" t="s">
         <v>71</v>
       </c>
       <c r="I58" s="1">
@@ -3119,7 +3129,7 @@
       <c r="G59" s="6">
         <v>868</v>
       </c>
-      <c r="H59" s="22" t="s">
+      <c r="H59" s="24" t="s">
         <v>55</v>
       </c>
       <c r="I59" s="2">
@@ -3152,7 +3162,7 @@
       <c r="G60" s="6">
         <v>4052</v>
       </c>
-      <c r="H60" s="22" t="s">
+      <c r="H60" s="24" t="s">
         <v>6</v>
       </c>
       <c r="I60" s="2">
@@ -3185,11 +3195,11 @@
       <c r="G61" s="6">
         <v>714</v>
       </c>
-      <c r="H61" s="22" t="s">
+      <c r="H61" s="23" t="s">
         <v>56</v>
       </c>
       <c r="I61" s="1">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="J61" s="3" t="str">
         <f t="shared" si="0"/>
@@ -3218,7 +3228,7 @@
       <c r="G62" s="6">
         <v>427</v>
       </c>
-      <c r="H62" s="22" t="s">
+      <c r="H62" s="24" t="s">
         <v>31</v>
       </c>
       <c r="I62" s="2">
@@ -3251,11 +3261,11 @@
       <c r="G63" s="6">
         <v>973</v>
       </c>
-      <c r="H63" s="22" t="s">
+      <c r="H63" s="23" t="s">
         <v>32</v>
       </c>
       <c r="I63" s="1">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="J63" s="3" t="str">
         <f t="shared" si="0"/>
@@ -3284,7 +3294,7 @@
       <c r="G64" s="6">
         <v>325</v>
       </c>
-      <c r="H64" s="22" t="s">
+      <c r="H64" s="23" t="s">
         <v>115</v>
       </c>
       <c r="I64" s="1">
@@ -3317,7 +3327,7 @@
       <c r="G65" s="6">
         <v>1296</v>
       </c>
-      <c r="H65" s="22" t="s">
+      <c r="H65" s="24" t="s">
         <v>33</v>
       </c>
       <c r="I65" s="2">
@@ -3350,11 +3360,11 @@
       <c r="G66" s="6">
         <v>227</v>
       </c>
-      <c r="H66" s="22" t="s">
+      <c r="H66" s="24" t="s">
         <v>57</v>
       </c>
       <c r="I66" s="2">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="J66" s="3" t="str">
         <f t="shared" si="0"/>
@@ -3383,7 +3393,7 @@
       <c r="G67" s="6">
         <v>2665</v>
       </c>
-      <c r="H67" s="22" t="s">
+      <c r="H67" s="24" t="s">
         <v>72</v>
       </c>
       <c r="I67" s="2">
@@ -3416,7 +3426,7 @@
       <c r="G68" s="6">
         <v>1189</v>
       </c>
-      <c r="H68" s="22" t="s">
+      <c r="H68" s="23" t="s">
         <v>34</v>
       </c>
       <c r="I68" s="1">
@@ -3449,11 +3459,11 @@
       <c r="G69" s="6">
         <v>142</v>
       </c>
-      <c r="H69" s="22" t="s">
+      <c r="H69" s="24" t="s">
         <v>35</v>
       </c>
       <c r="I69" s="2">
-        <v>70</v>
+        <v>95</v>
       </c>
       <c r="J69" s="3" t="str">
         <f t="shared" si="1"/>
@@ -3482,7 +3492,7 @@
       <c r="G70" s="6">
         <v>1500</v>
       </c>
-      <c r="H70" s="22" t="s">
+      <c r="H70" s="23" t="s">
         <v>36</v>
       </c>
       <c r="I70" s="1">
@@ -3515,7 +3525,7 @@
       <c r="G71" s="6">
         <v>1189</v>
       </c>
-      <c r="H71" s="22" t="s">
+      <c r="H71" s="24" t="s">
         <v>37</v>
       </c>
       <c r="I71" s="2">
@@ -3548,7 +3558,7 @@
       <c r="G72" s="6">
         <v>728</v>
       </c>
-      <c r="H72" s="22" t="s">
+      <c r="H72" s="23" t="s">
         <v>38</v>
       </c>
       <c r="I72" s="1">
@@ -3581,7 +3591,7 @@
       <c r="G73" s="6">
         <v>745</v>
       </c>
-      <c r="H73" s="22" t="s">
+      <c r="H73" s="23" t="s">
         <v>73</v>
       </c>
       <c r="I73" s="1">
@@ -3614,7 +3624,7 @@
       <c r="G74" s="6">
         <v>3547</v>
       </c>
-      <c r="H74" s="22" t="s">
+      <c r="H74" s="23" t="s">
         <v>7</v>
       </c>
       <c r="I74" s="1">
@@ -3647,11 +3657,11 @@
       <c r="G75" s="6">
         <v>421</v>
       </c>
-      <c r="H75" s="22" t="s">
+      <c r="H75" s="24" t="s">
         <v>7</v>
       </c>
       <c r="I75" s="2">
-        <v>17</v>
+        <v>37</v>
       </c>
       <c r="J75" s="3" t="str">
         <f t="shared" si="1"/>
@@ -3680,11 +3690,11 @@
       <c r="G76" s="6">
         <v>204</v>
       </c>
-      <c r="H76" s="22" t="s">
+      <c r="H76" s="23" t="s">
         <v>91</v>
       </c>
       <c r="I76" s="1">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="J76" s="3" t="str">
         <f t="shared" si="1"/>
@@ -3713,7 +3723,7 @@
       <c r="G77" s="6">
         <v>2922</v>
       </c>
-      <c r="H77" s="22" t="s">
+      <c r="H77" s="24" t="s">
         <v>8</v>
       </c>
       <c r="I77" s="2">
@@ -3746,7 +3756,7 @@
       <c r="G78" s="6">
         <v>4254</v>
       </c>
-      <c r="H78" s="22" t="s">
+      <c r="H78" s="24" t="s">
         <v>39</v>
       </c>
       <c r="I78" s="2">
@@ -3779,11 +3789,11 @@
       <c r="G79" s="17">
         <v>281</v>
       </c>
-      <c r="H79" s="22" t="s">
+      <c r="H79" s="23" t="s">
         <v>116</v>
       </c>
       <c r="I79" s="1">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="J79" s="3" t="str">
         <f t="shared" si="1"/>
@@ -3812,7 +3822,7 @@
       <c r="G80" s="6">
         <v>1528</v>
       </c>
-      <c r="H80" s="22" t="s">
+      <c r="H80" s="23" t="s">
         <v>58</v>
       </c>
       <c r="I80" s="1">
@@ -3845,7 +3855,7 @@
       <c r="G81" s="6">
         <v>550</v>
       </c>
-      <c r="H81" s="22" t="s">
+      <c r="H81" s="24" t="s">
         <v>59</v>
       </c>
       <c r="I81" s="2">
@@ -3878,11 +3888,11 @@
       <c r="G82" s="6">
         <v>1767</v>
       </c>
-      <c r="H82" s="22" t="s">
+      <c r="H82" s="23" t="s">
         <v>40</v>
       </c>
       <c r="I82" s="1">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="J82" s="3" t="str">
         <f t="shared" si="1"/>
@@ -3911,7 +3921,7 @@
       <c r="G83" s="6">
         <v>4700</v>
       </c>
-      <c r="H83" s="22" t="s">
+      <c r="H83" s="24" t="s">
         <v>74</v>
       </c>
       <c r="I83" s="2">
@@ -3944,7 +3954,7 @@
       <c r="G84" s="6">
         <v>230</v>
       </c>
-      <c r="H84" s="22" t="s">
+      <c r="H84" s="24" t="s">
         <v>92</v>
       </c>
       <c r="I84" s="2">
@@ -3977,7 +3987,7 @@
       <c r="G85" s="6">
         <v>832</v>
       </c>
-      <c r="H85" s="22" t="s">
+      <c r="H85" s="24" t="s">
         <v>41</v>
       </c>
       <c r="I85" s="2">
@@ -4010,7 +4020,7 @@
       <c r="G86" s="6">
         <v>517</v>
       </c>
-      <c r="H86" s="22" t="s">
+      <c r="H86" s="24" t="s">
         <v>117</v>
       </c>
       <c r="I86" s="2">
@@ -4043,7 +4053,7 @@
       <c r="G87" s="6">
         <v>3159</v>
       </c>
-      <c r="H87" s="22" t="s">
+      <c r="H87" s="24" t="s">
         <v>2</v>
       </c>
       <c r="I87" s="2">
@@ -4076,11 +4086,11 @@
       <c r="G88" s="6">
         <v>1109</v>
       </c>
-      <c r="H88" s="22" t="s">
+      <c r="H88" s="23" t="s">
         <v>93</v>
       </c>
       <c r="I88" s="1">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="J88" s="3" t="str">
         <f t="shared" si="1"/>
@@ -4109,11 +4119,11 @@
       <c r="G89" s="6">
         <v>1145</v>
       </c>
-      <c r="H89" s="22" t="s">
+      <c r="H89" s="24" t="s">
         <v>94</v>
       </c>
       <c r="I89" s="2">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="J89" s="3" t="str">
         <f t="shared" si="1"/>
@@ -4142,11 +4152,11 @@
       <c r="G90" s="6">
         <v>3446</v>
       </c>
-      <c r="H90" s="22" t="s">
+      <c r="H90" s="23" t="s">
         <v>42</v>
       </c>
       <c r="I90" s="1">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="J90" s="3" t="str">
         <f t="shared" si="1"/>
@@ -4175,11 +4185,11 @@
       <c r="G91" s="6">
         <v>1879</v>
       </c>
-      <c r="H91" s="22" t="s">
+      <c r="H91" s="24" t="s">
         <v>43</v>
       </c>
       <c r="I91" s="2">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="J91" s="3" t="str">
         <f t="shared" si="1"/>
@@ -4208,7 +4218,7 @@
       <c r="G92" s="6">
         <v>627</v>
       </c>
-      <c r="H92" s="22" t="s">
+      <c r="H92" s="23" t="s">
         <v>44</v>
       </c>
       <c r="I92" s="1">
@@ -4241,7 +4251,7 @@
       <c r="G93" s="6">
         <v>1514</v>
       </c>
-      <c r="H93" s="22" t="s">
+      <c r="H93" s="23" t="s">
         <v>75</v>
       </c>
       <c r="I93" s="1">
@@ -4274,7 +4284,7 @@
       <c r="G94" s="6">
         <v>166</v>
       </c>
-      <c r="H94" s="22" t="s">
+      <c r="H94" s="23" t="s">
         <v>118</v>
       </c>
       <c r="I94" s="1">
@@ -4307,7 +4317,7 @@
       <c r="G95" s="6">
         <v>4884</v>
       </c>
-      <c r="H95" s="22" t="s">
+      <c r="H95" s="24" t="s">
         <v>45</v>
       </c>
       <c r="I95" s="2">
@@ -4340,11 +4350,11 @@
       <c r="G96" s="6">
         <v>3558</v>
       </c>
-      <c r="H96" s="22" t="s">
+      <c r="H96" s="23" t="s">
         <v>9</v>
       </c>
       <c r="I96" s="1">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="J96" s="3" t="str">
         <f t="shared" si="1"/>
@@ -4373,7 +4383,7 @@
       <c r="G97" s="6">
         <v>1191</v>
       </c>
-      <c r="H97" s="22" t="s">
+      <c r="H97" s="24" t="s">
         <v>76</v>
       </c>
       <c r="I97" s="2">
@@ -4406,7 +4416,7 @@
       <c r="G98" s="6">
         <v>2506</v>
       </c>
-      <c r="H98" s="22" t="s">
+      <c r="H98" s="23" t="s">
         <v>95</v>
       </c>
       <c r="I98" s="1">
@@ -4439,11 +4449,11 @@
       <c r="G99" s="6">
         <v>32</v>
       </c>
-      <c r="H99" s="22" t="s">
+      <c r="H99" s="23" t="s">
         <v>77</v>
       </c>
       <c r="I99" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J99" s="3" t="str">
         <f t="shared" si="1"/>
@@ -4472,11 +4482,11 @@
       <c r="G100" s="6">
         <v>2345</v>
       </c>
-      <c r="H100" s="22" t="s">
+      <c r="H100" s="24" t="s">
         <v>96</v>
       </c>
       <c r="I100" s="2">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="J100" s="3" t="str">
         <f t="shared" si="1"/>
@@ -4505,11 +4515,11 @@
       <c r="G101" s="6">
         <v>6268</v>
       </c>
-      <c r="H101" s="22" t="s">
+      <c r="H101" s="23" t="s">
         <v>97</v>
       </c>
       <c r="I101" s="1">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="J101" s="3" t="str">
         <f t="shared" si="1"/>
@@ -4538,7 +4548,7 @@
       <c r="G102" s="6">
         <v>382</v>
       </c>
-      <c r="H102" s="22" t="s">
+      <c r="H102" s="23" t="s">
         <v>3</v>
       </c>
       <c r="I102" s="1">
@@ -4571,7 +4581,7 @@
       <c r="G103" s="6">
         <v>3363</v>
       </c>
-      <c r="H103" s="22" t="s">
+      <c r="H103" s="24" t="s">
         <v>78</v>
       </c>
       <c r="I103" s="2">
@@ -4604,11 +4614,11 @@
       <c r="G104" s="6">
         <v>633</v>
       </c>
-      <c r="H104" s="22" t="s">
+      <c r="H104" s="24" t="s">
         <v>119</v>
       </c>
       <c r="I104" s="2">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="J104" s="3" t="str">
         <f t="shared" si="1"/>
@@ -4637,11 +4647,11 @@
       <c r="G105" s="6">
         <v>2855</v>
       </c>
-      <c r="H105" s="22" t="s">
+      <c r="H105" s="24" t="s">
         <v>98</v>
       </c>
       <c r="I105" s="2">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="J105" s="3" t="str">
         <f t="shared" si="1"/>
@@ -4670,11 +4680,11 @@
       <c r="G106" s="6">
         <v>988</v>
       </c>
-      <c r="H106" s="22" t="s">
+      <c r="H106" s="23" t="s">
         <v>79</v>
       </c>
       <c r="I106" s="1">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J106" s="3" t="str">
         <f t="shared" si="1"/>
@@ -4703,11 +4713,11 @@
       <c r="G107" s="6">
         <v>676</v>
       </c>
-      <c r="H107" s="22" t="s">
+      <c r="H107" s="23" t="s">
         <v>99</v>
       </c>
       <c r="I107" s="1">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="J107" s="3" t="str">
         <f t="shared" si="1"/>
@@ -4736,7 +4746,7 @@
       <c r="G108" s="6">
         <v>2448</v>
       </c>
-      <c r="H108" s="22" t="s">
+      <c r="H108" s="24" t="s">
         <v>80</v>
       </c>
       <c r="I108" s="2">
@@ -4769,11 +4779,11 @@
       <c r="G109" s="6">
         <v>2327</v>
       </c>
-      <c r="H109" s="22" t="s">
+      <c r="H109" s="23" t="s">
         <v>60</v>
       </c>
       <c r="I109" s="1">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="J109" s="3" t="str">
         <f t="shared" si="1"/>
@@ -4802,11 +4812,11 @@
       <c r="G110" s="6">
         <v>201</v>
       </c>
-      <c r="H110" s="22" t="s">
+      <c r="H110" s="23" t="s">
         <v>46</v>
       </c>
       <c r="I110" s="1">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="J110" s="3" t="str">
         <f t="shared" si="1"/>
@@ -4835,11 +4845,11 @@
       <c r="G111" s="6">
         <v>658</v>
       </c>
-      <c r="H111" s="22" t="s">
+      <c r="H111" s="24" t="s">
         <v>100</v>
       </c>
       <c r="I111" s="2">
-        <v>5</v>
+        <v>28</v>
       </c>
       <c r="J111" s="3" t="str">
         <f t="shared" si="1"/>
@@ -4868,7 +4878,7 @@
       <c r="G112" s="6">
         <v>1013</v>
       </c>
-      <c r="H112" s="22" t="s">
+      <c r="H112" s="24" t="s">
         <v>47</v>
       </c>
       <c r="I112" s="2">
@@ -4901,11 +4911,11 @@
       <c r="G113" s="6">
         <v>980</v>
       </c>
-      <c r="H113" s="22" t="s">
+      <c r="H113" s="23" t="s">
         <v>101</v>
       </c>
       <c r="I113" s="1">
-        <v>14</v>
+        <v>62</v>
       </c>
       <c r="J113" s="3" t="str">
         <f t="shared" si="1"/>
@@ -4934,7 +4944,7 @@
       <c r="G114" s="6">
         <v>2780</v>
       </c>
-      <c r="H114" s="22" t="s">
+      <c r="H114" s="23" t="s">
         <v>48</v>
       </c>
       <c r="I114" s="1">
@@ -4967,7 +4977,7 @@
       <c r="G115" s="6">
         <v>565</v>
       </c>
-      <c r="H115" s="22" t="s">
+      <c r="H115" s="24" t="s">
         <v>49</v>
       </c>
       <c r="I115" s="2">
@@ -5000,11 +5010,11 @@
       <c r="G116" s="6">
         <v>139</v>
       </c>
-      <c r="H116" s="22" t="s">
+      <c r="H116" s="23" t="s">
         <v>81</v>
       </c>
       <c r="I116" s="1">
-        <v>6</v>
+        <v>31</v>
       </c>
       <c r="J116" s="3" t="str">
         <f t="shared" si="1"/>
@@ -5033,7 +5043,7 @@
       <c r="G117" s="6">
         <v>1948</v>
       </c>
-      <c r="H117" s="22" t="s">
+      <c r="H117" s="24" t="s">
         <v>102</v>
       </c>
       <c r="I117" s="2">
@@ -5066,7 +5076,7 @@
       <c r="G118" s="6">
         <v>1652</v>
       </c>
-      <c r="H118" s="22" t="s">
+      <c r="H118" s="24" t="s">
         <v>82</v>
       </c>
       <c r="I118" s="2">
@@ -5099,7 +5109,7 @@
       <c r="G119" s="6">
         <v>899</v>
       </c>
-      <c r="H119" s="22" t="s">
+      <c r="H119" s="23" t="s">
         <v>103</v>
       </c>
       <c r="I119" s="1">
@@ -5132,11 +5142,11 @@
       <c r="G120" s="6">
         <v>2509</v>
       </c>
-      <c r="H120" s="22" t="s">
+      <c r="H120" s="23" t="s">
         <v>50</v>
       </c>
       <c r="I120" s="1">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="J120" s="3" t="str">
         <f t="shared" si="1"/>
@@ -5165,7 +5175,7 @@
       <c r="G121" s="6">
         <v>128</v>
       </c>
-      <c r="H121" s="22" t="s">
+      <c r="H121" s="23" t="s">
         <v>120</v>
       </c>
       <c r="I121" s="1">
@@ -5198,7 +5208,7 @@
       <c r="G122" s="6">
         <v>1015</v>
       </c>
-      <c r="H122" s="22" t="s">
+      <c r="H122" s="24" t="s">
         <v>51</v>
       </c>
       <c r="I122" s="2">
@@ -5231,11 +5241,11 @@
       <c r="G123" s="6">
         <v>402</v>
       </c>
-      <c r="H123" s="22" t="s">
+      <c r="H123" s="24" t="s">
         <v>104</v>
       </c>
       <c r="I123" s="2">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="J123" s="3" t="str">
         <f t="shared" si="1"/>
@@ -5264,7 +5274,7 @@
       <c r="G124" s="6">
         <v>192</v>
       </c>
-      <c r="H124" s="22" t="s">
+      <c r="H124" s="24" t="s">
         <v>121</v>
       </c>
       <c r="I124" s="2">
@@ -5297,11 +5307,11 @@
       <c r="G125" s="6">
         <v>618</v>
       </c>
-      <c r="H125" s="22" t="s">
+      <c r="H125" s="23" t="s">
         <v>83</v>
       </c>
       <c r="I125" s="1">
-        <v>19</v>
+        <v>39</v>
       </c>
       <c r="J125" s="3" t="str">
         <f t="shared" si="1"/>
@@ -5329,10 +5339,10 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="19.140625" customWidth="1"/>
-    <col min="4" max="4" width="27.28515625" customWidth="1"/>
+    <col min="4" max="4" width="18.42578125" customWidth="1"/>
     <col min="5" max="5" width="14" customWidth="1"/>
     <col min="6" max="6" width="14.140625" customWidth="1"/>
-    <col min="8" max="8" width="17" style="23" customWidth="1"/>
+    <col min="8" max="8" width="17" style="22" customWidth="1"/>
     <col min="9" max="9" width="13.42578125" customWidth="1"/>
   </cols>
   <sheetData>
@@ -5390,11 +5400,11 @@
       <c r="G2" s="6">
         <v>3312</v>
       </c>
-      <c r="H2" s="22" t="s">
+      <c r="H2" s="27" t="s">
         <v>1</v>
       </c>
-      <c r="I2" s="1">
-        <v>33</v>
+      <c r="I2" s="28">
+        <v>44</v>
       </c>
       <c r="J2" s="3" t="str">
         <f>IF(C2=H2,"Match","Different")</f>
@@ -5423,7 +5433,7 @@
       <c r="G3" s="6">
         <v>3159</v>
       </c>
-      <c r="H3" s="22" t="s">
+      <c r="H3" s="24" t="s">
         <v>2</v>
       </c>
       <c r="I3" s="2">
@@ -5456,7 +5466,7 @@
       <c r="G4" s="6">
         <v>382</v>
       </c>
-      <c r="H4" s="22" t="s">
+      <c r="H4" s="23" t="s">
         <v>3</v>
       </c>
       <c r="I4" s="1">
@@ -5489,11 +5499,11 @@
       <c r="G5" s="6">
         <v>6138</v>
       </c>
-      <c r="H5" s="22" t="s">
+      <c r="H5" s="24" t="s">
         <v>4</v>
       </c>
       <c r="I5" s="2">
-        <v>4</v>
+        <v>42</v>
       </c>
       <c r="J5" s="3" t="str">
         <f>IF(C5=H5,"Match","Different")</f>
@@ -5522,11 +5532,11 @@
       <c r="G6" s="6">
         <v>2204</v>
       </c>
-      <c r="H6" s="22" t="s">
+      <c r="H6" s="23" t="s">
         <v>5</v>
       </c>
       <c r="I6" s="1">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="J6" s="3" t="str">
         <f>IF(C6=H6,"Match","Different")</f>
@@ -5555,7 +5565,7 @@
       <c r="G7" s="6">
         <v>4052</v>
       </c>
-      <c r="H7" s="22" t="s">
+      <c r="H7" s="24" t="s">
         <v>6</v>
       </c>
       <c r="I7" s="2">
@@ -5588,7 +5598,7 @@
       <c r="G8" s="6">
         <v>3547</v>
       </c>
-      <c r="H8" s="22" t="s">
+      <c r="H8" s="23" t="s">
         <v>7</v>
       </c>
       <c r="I8" s="1">
@@ -5621,7 +5631,7 @@
       <c r="G9" s="6">
         <v>2922</v>
       </c>
-      <c r="H9" s="22" t="s">
+      <c r="H9" s="24" t="s">
         <v>8</v>
       </c>
       <c r="I9" s="2">
@@ -5654,11 +5664,11 @@
       <c r="G10" s="6">
         <v>3558</v>
       </c>
-      <c r="H10" s="22" t="s">
+      <c r="H10" s="23" t="s">
         <v>9</v>
       </c>
       <c r="I10" s="1">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="J10" s="3" t="str">
         <f>IF(C10=H10,"Match","Different")</f>
@@ -5687,7 +5697,7 @@
       <c r="G11" s="6">
         <v>739</v>
       </c>
-      <c r="H11" s="22" t="s">
+      <c r="H11" s="24" t="s">
         <v>10</v>
       </c>
       <c r="I11" s="2">
@@ -5720,7 +5730,7 @@
       <c r="G12" s="6">
         <v>1066</v>
       </c>
-      <c r="H12" s="22" t="s">
+      <c r="H12" s="23" t="s">
         <v>11</v>
       </c>
       <c r="I12" s="1">
@@ -5753,7 +5763,7 @@
       <c r="G13" s="6">
         <v>1628</v>
       </c>
-      <c r="H13" s="22" t="s">
+      <c r="H13" s="24" t="s">
         <v>12</v>
       </c>
       <c r="I13" s="2">
@@ -5786,7 +5796,7 @@
       <c r="G14" s="6">
         <v>3909</v>
       </c>
-      <c r="H14" s="22" t="s">
+      <c r="H14" s="23" t="s">
         <v>13</v>
       </c>
       <c r="I14" s="1">
@@ -5819,7 +5829,7 @@
       <c r="G15" s="6">
         <v>1162</v>
       </c>
-      <c r="H15" s="22" t="s">
+      <c r="H15" s="24" t="s">
         <v>14</v>
       </c>
       <c r="I15" s="2">
@@ -5852,7 +5862,7 @@
       <c r="G16" s="6">
         <v>1336</v>
       </c>
-      <c r="H16" s="22" t="s">
+      <c r="H16" s="23" t="s">
         <v>15</v>
       </c>
       <c r="I16" s="1">
@@ -5885,7 +5895,7 @@
       <c r="G17" s="6">
         <v>4783</v>
       </c>
-      <c r="H17" s="22" t="s">
+      <c r="H17" s="24" t="s">
         <v>0</v>
       </c>
       <c r="I17" s="2">
@@ -5918,7 +5928,7 @@
       <c r="G18" s="6">
         <v>570</v>
       </c>
-      <c r="H18" s="22" t="s">
+      <c r="H18" s="23" t="s">
         <v>16</v>
       </c>
       <c r="I18" s="1">
@@ -5951,7 +5961,7 @@
       <c r="G19" s="6">
         <v>5202</v>
       </c>
-      <c r="H19" s="22" t="s">
+      <c r="H19" s="24" t="s">
         <v>17</v>
       </c>
       <c r="I19" s="2">
@@ -5984,7 +5994,7 @@
       <c r="G20" s="6">
         <v>902</v>
       </c>
-      <c r="H20" s="22" t="s">
+      <c r="H20" s="23" t="s">
         <v>18</v>
       </c>
       <c r="I20" s="1">
@@ -6017,7 +6027,7 @@
       <c r="G21" s="6">
         <v>257</v>
       </c>
-      <c r="H21" s="22" t="s">
+      <c r="H21" s="24" t="s">
         <v>19</v>
       </c>
       <c r="I21" s="2">
@@ -6050,11 +6060,11 @@
       <c r="G22" s="6">
         <v>303</v>
       </c>
-      <c r="H22" s="22" t="s">
+      <c r="H22" s="24" t="s">
         <v>21</v>
       </c>
       <c r="I22" s="2">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="J22" s="3" t="str">
         <f>IF(C22=H22,"Match","Different")</f>
@@ -6083,11 +6093,11 @@
       <c r="G23" s="6">
         <v>525</v>
       </c>
-      <c r="H23" s="22" t="s">
+      <c r="H23" s="23" t="s">
         <v>20</v>
       </c>
       <c r="I23" s="1">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="J23" s="3" t="str">
         <f>IF(C23=H23,"Match","Different")</f>
@@ -6116,7 +6126,7 @@
       <c r="G24" s="6">
         <v>3473</v>
       </c>
-      <c r="H24" s="22" t="s">
+      <c r="H24" s="23" t="s">
         <v>22</v>
       </c>
       <c r="I24" s="1">
@@ -6149,11 +6159,11 @@
       <c r="G25" s="6">
         <v>1450</v>
       </c>
-      <c r="H25" s="22" t="s">
+      <c r="H25" s="24" t="s">
         <v>23</v>
       </c>
       <c r="I25" s="2">
-        <v>16</v>
+        <v>41</v>
       </c>
       <c r="J25" s="3" t="str">
         <f>IF(C25=H25,"Match","Different")</f>
@@ -6182,11 +6192,11 @@
       <c r="G26" s="6">
         <v>698</v>
       </c>
-      <c r="H26" s="22" t="s">
+      <c r="H26" s="23" t="s">
         <v>24</v>
       </c>
       <c r="I26" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J26" s="3" t="str">
         <f>IF(C26=H26,"Match","Different")</f>
@@ -6215,7 +6225,7 @@
       <c r="G27" s="6">
         <v>676</v>
       </c>
-      <c r="H27" s="22" t="s">
+      <c r="H27" s="24" t="s">
         <v>25</v>
       </c>
       <c r="I27" s="2">
@@ -6237,7 +6247,7 @@
         <v>26</v>
       </c>
       <c r="D28" s="7" t="s">
-        <v>217</v>
+        <v>178</v>
       </c>
       <c r="E28" s="5" t="s">
         <v>141</v>
@@ -6248,11 +6258,11 @@
       <c r="G28" s="6">
         <v>2966</v>
       </c>
-      <c r="H28" s="22" t="s">
+      <c r="H28" s="23" t="s">
         <v>26</v>
       </c>
       <c r="I28" s="1">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="J28" s="3" t="str">
         <f>IF(C28=H28,"Match","Different")</f>
@@ -6281,7 +6291,7 @@
       <c r="G29" s="6">
         <v>691</v>
       </c>
-      <c r="H29" s="22" t="s">
+      <c r="H29" s="24" t="s">
         <v>27</v>
       </c>
       <c r="I29" s="2">
@@ -6314,7 +6324,7 @@
       <c r="G30" s="6">
         <v>643</v>
       </c>
-      <c r="H30" s="22" t="s">
+      <c r="H30" s="24" t="s">
         <v>29</v>
       </c>
       <c r="I30" s="2">
@@ -6347,7 +6357,7 @@
       <c r="G31" s="6">
         <v>1366</v>
       </c>
-      <c r="H31" s="22" t="s">
+      <c r="H31" s="23" t="s">
         <v>28</v>
       </c>
       <c r="I31" s="1">
@@ -6380,7 +6390,7 @@
       <c r="G32" s="6">
         <v>4570</v>
       </c>
-      <c r="H32" s="22" t="s">
+      <c r="H32" s="23" t="s">
         <v>30</v>
       </c>
       <c r="I32" s="1">
@@ -6413,7 +6423,7 @@
       <c r="G33" s="6">
         <v>427</v>
       </c>
-      <c r="H33" s="22" t="s">
+      <c r="H33" s="24" t="s">
         <v>31</v>
       </c>
       <c r="I33" s="2">
@@ -6446,11 +6456,11 @@
       <c r="G34" s="6">
         <v>973</v>
       </c>
-      <c r="H34" s="22" t="s">
+      <c r="H34" s="23" t="s">
         <v>32</v>
       </c>
       <c r="I34" s="1">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="J34" s="3" t="str">
         <f>IF(C34=H34,"Match","Different")</f>
@@ -6479,7 +6489,7 @@
       <c r="G35" s="6">
         <v>1296</v>
       </c>
-      <c r="H35" s="22" t="s">
+      <c r="H35" s="24" t="s">
         <v>33</v>
       </c>
       <c r="I35" s="2">
@@ -6512,7 +6522,7 @@
       <c r="G36" s="6">
         <v>1189</v>
       </c>
-      <c r="H36" s="22" t="s">
+      <c r="H36" s="23" t="s">
         <v>34</v>
       </c>
       <c r="I36" s="1">
@@ -6545,11 +6555,11 @@
       <c r="G37" s="6">
         <v>142</v>
       </c>
-      <c r="H37" s="22" t="s">
+      <c r="H37" s="24" t="s">
         <v>35</v>
       </c>
       <c r="I37" s="2">
-        <v>70</v>
+        <v>95</v>
       </c>
       <c r="J37" s="3" t="str">
         <f>IF(C37=H37,"Match","Different")</f>
@@ -6578,7 +6588,7 @@
       <c r="G38" s="6">
         <v>1500</v>
       </c>
-      <c r="H38" s="22" t="s">
+      <c r="H38" s="23" t="s">
         <v>36</v>
       </c>
       <c r="I38" s="1">
@@ -6611,7 +6621,7 @@
       <c r="G39" s="6">
         <v>1189</v>
       </c>
-      <c r="H39" s="22" t="s">
+      <c r="H39" s="24" t="s">
         <v>37</v>
       </c>
       <c r="I39" s="2">
@@ -6644,7 +6654,7 @@
       <c r="G40" s="6">
         <v>728</v>
       </c>
-      <c r="H40" s="22" t="s">
+      <c r="H40" s="23" t="s">
         <v>38</v>
       </c>
       <c r="I40" s="1">
@@ -6677,7 +6687,7 @@
       <c r="G41" s="6">
         <v>4254</v>
       </c>
-      <c r="H41" s="22" t="s">
+      <c r="H41" s="24" t="s">
         <v>39</v>
       </c>
       <c r="I41" s="2">
@@ -6710,11 +6720,11 @@
       <c r="G42" s="6">
         <v>1767</v>
       </c>
-      <c r="H42" s="22" t="s">
+      <c r="H42" s="23" t="s">
         <v>40</v>
       </c>
       <c r="I42" s="1">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="J42" s="3" t="str">
         <f>IF(C42=H42,"Match","Different")</f>
@@ -6743,7 +6753,7 @@
       <c r="G43" s="6">
         <v>832</v>
       </c>
-      <c r="H43" s="22" t="s">
+      <c r="H43" s="24" t="s">
         <v>41</v>
       </c>
       <c r="I43" s="2">
@@ -6765,7 +6775,7 @@
         <v>42</v>
       </c>
       <c r="D44" s="7" t="s">
-        <v>218</v>
+        <v>190</v>
       </c>
       <c r="E44" s="7" t="s">
         <v>129</v>
@@ -6776,11 +6786,11 @@
       <c r="G44" s="6">
         <v>3446</v>
       </c>
-      <c r="H44" s="22" t="s">
+      <c r="H44" s="23" t="s">
         <v>42</v>
       </c>
       <c r="I44" s="1">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="J44" s="3" t="str">
         <f>IF(C44=H44,"Match","Different")</f>
@@ -6809,11 +6819,11 @@
       <c r="G45" s="6">
         <v>1879</v>
       </c>
-      <c r="H45" s="22" t="s">
+      <c r="H45" s="24" t="s">
         <v>43</v>
       </c>
       <c r="I45" s="2">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="J45" s="3" t="str">
         <f>IF(C45=H45,"Match","Different")</f>
@@ -6842,7 +6852,7 @@
       <c r="G46" s="6">
         <v>627</v>
       </c>
-      <c r="H46" s="22" t="s">
+      <c r="H46" s="23" t="s">
         <v>44</v>
       </c>
       <c r="I46" s="1">
@@ -6875,7 +6885,7 @@
       <c r="G47" s="6">
         <v>4884</v>
       </c>
-      <c r="H47" s="22" t="s">
+      <c r="H47" s="24" t="s">
         <v>45</v>
       </c>
       <c r="I47" s="2">
@@ -6908,11 +6918,11 @@
       <c r="G48" s="6">
         <v>201</v>
       </c>
-      <c r="H48" s="22" t="s">
+      <c r="H48" s="23" t="s">
         <v>46</v>
       </c>
       <c r="I48" s="1">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="J48" s="3" t="str">
         <f>IF(C48=H48,"Match","Different")</f>
@@ -6941,7 +6951,7 @@
       <c r="G49" s="6">
         <v>1013</v>
       </c>
-      <c r="H49" s="22" t="s">
+      <c r="H49" s="24" t="s">
         <v>47</v>
       </c>
       <c r="I49" s="2">
@@ -6974,7 +6984,7 @@
       <c r="G50" s="6">
         <v>2780</v>
       </c>
-      <c r="H50" s="22" t="s">
+      <c r="H50" s="23" t="s">
         <v>48</v>
       </c>
       <c r="I50" s="1">
@@ -7007,7 +7017,7 @@
       <c r="G51" s="6">
         <v>565</v>
       </c>
-      <c r="H51" s="22" t="s">
+      <c r="H51" s="24" t="s">
         <v>49</v>
       </c>
       <c r="I51" s="2">
@@ -7040,11 +7050,11 @@
       <c r="G52" s="6">
         <v>2509</v>
       </c>
-      <c r="H52" s="22" t="s">
+      <c r="H52" s="23" t="s">
         <v>50</v>
       </c>
       <c r="I52" s="1">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="J52" s="3" t="str">
         <f>IF(C52=H52,"Match","Different")</f>
@@ -7073,7 +7083,7 @@
       <c r="G53" s="6">
         <v>1015</v>
       </c>
-      <c r="H53" s="22" t="s">
+      <c r="H53" s="24" t="s">
         <v>51</v>
       </c>
       <c r="I53" s="2">
@@ -7106,7 +7116,7 @@
       <c r="G54" s="6">
         <v>1943</v>
       </c>
-      <c r="H54" s="22" t="s">
+      <c r="H54" s="23" t="s">
         <v>52</v>
       </c>
       <c r="I54" s="1">
@@ -7139,11 +7149,11 @@
       <c r="G55" s="6">
         <v>1172</v>
       </c>
-      <c r="H55" s="22" t="s">
+      <c r="H55" s="24" t="s">
         <v>53</v>
       </c>
       <c r="I55" s="2">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="J55" s="3" t="str">
         <f>IF(C55=H55,"Match","Different")</f>
@@ -7161,7 +7171,7 @@
         <v>54</v>
       </c>
       <c r="D56" s="8" t="s">
-        <v>191</v>
+        <v>180</v>
       </c>
       <c r="E56" s="9" t="s">
         <v>154</v>
@@ -7172,7 +7182,7 @@
       <c r="G56" s="6">
         <v>1275</v>
       </c>
-      <c r="H56" s="22" t="s">
+      <c r="H56" s="23" t="s">
         <v>54</v>
       </c>
       <c r="I56" s="1">
@@ -7205,7 +7215,7 @@
       <c r="G57" s="6">
         <v>868</v>
       </c>
-      <c r="H57" s="22" t="s">
+      <c r="H57" s="24" t="s">
         <v>55</v>
       </c>
       <c r="I57" s="2">
@@ -7238,11 +7248,11 @@
       <c r="G58" s="6">
         <v>714</v>
       </c>
-      <c r="H58" s="22" t="s">
+      <c r="H58" s="23" t="s">
         <v>56</v>
       </c>
       <c r="I58" s="1">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="J58" s="3" t="str">
         <f>IF(C58=H58,"Match","Different")</f>
@@ -7260,7 +7270,7 @@
         <v>57</v>
       </c>
       <c r="D59" s="8" t="s">
-        <v>191</v>
+        <v>180</v>
       </c>
       <c r="E59" s="9" t="s">
         <v>154</v>
@@ -7271,11 +7281,11 @@
       <c r="G59" s="6">
         <v>227</v>
       </c>
-      <c r="H59" s="22" t="s">
+      <c r="H59" s="24" t="s">
         <v>57</v>
       </c>
       <c r="I59" s="2">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="J59" s="3" t="str">
         <f>IF(C59=H59,"Match","Different")</f>
@@ -7304,7 +7314,7 @@
       <c r="G60" s="6">
         <v>1528</v>
       </c>
-      <c r="H60" s="22" t="s">
+      <c r="H60" s="23" t="s">
         <v>58</v>
       </c>
       <c r="I60" s="1">
@@ -7337,7 +7347,7 @@
       <c r="G61" s="6">
         <v>550</v>
       </c>
-      <c r="H61" s="22" t="s">
+      <c r="H61" s="24" t="s">
         <v>59</v>
       </c>
       <c r="I61" s="2">
@@ -7370,11 +7380,11 @@
       <c r="G62" s="6">
         <v>2327</v>
       </c>
-      <c r="H62" s="22" t="s">
+      <c r="H62" s="23" t="s">
         <v>60</v>
       </c>
       <c r="I62" s="1">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="J62" s="3" t="str">
         <f>IF(C62=H62,"Match","Different")</f>
@@ -7403,7 +7413,7 @@
       <c r="G63" s="6">
         <v>2940</v>
       </c>
-      <c r="H63" s="22" t="s">
+      <c r="H63" s="24" t="s">
         <v>62</v>
       </c>
       <c r="I63" s="2">
@@ -7436,7 +7446,7 @@
       <c r="G64" s="6">
         <v>1429</v>
       </c>
-      <c r="H64" s="22" t="s">
+      <c r="H64" s="23" t="s">
         <v>63</v>
       </c>
       <c r="I64" s="1">
@@ -7469,11 +7479,11 @@
       <c r="G65" s="6">
         <v>19</v>
       </c>
-      <c r="H65" s="22" t="s">
+      <c r="H65" s="24" t="s">
         <v>64</v>
       </c>
       <c r="I65" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J65" s="3" t="str">
         <f>IF(C65=H65,"Match","Different")</f>
@@ -7502,11 +7512,11 @@
       <c r="G66" s="6">
         <v>829</v>
       </c>
-      <c r="H66" s="22" t="s">
+      <c r="H66" s="23" t="s">
         <v>54</v>
       </c>
       <c r="I66" s="1">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="J66" s="3" t="str">
         <f>IF(C66=H66,"Match","Different")</f>
@@ -7535,11 +7545,11 @@
       <c r="G67" s="6">
         <v>830</v>
       </c>
-      <c r="H67" s="22" t="s">
+      <c r="H67" s="23" t="s">
         <v>66</v>
       </c>
       <c r="I67" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J67" s="3" t="str">
         <f>IF(C67=H67,"Match","Different")</f>
@@ -7568,7 +7578,7 @@
       <c r="G68" s="6">
         <v>1485</v>
       </c>
-      <c r="H68" s="22" t="s">
+      <c r="H68" s="24" t="s">
         <v>67</v>
       </c>
       <c r="I68" s="2">
@@ -7601,7 +7611,7 @@
       <c r="G69" s="6">
         <v>6</v>
       </c>
-      <c r="H69" s="22" t="s">
+      <c r="H69" s="24" t="s">
         <v>69</v>
       </c>
       <c r="I69" s="2">
@@ -7634,11 +7644,11 @@
       <c r="G70" s="6">
         <v>2909</v>
       </c>
-      <c r="H70" s="22" t="s">
+      <c r="H70" s="23" t="s">
         <v>70</v>
       </c>
       <c r="I70" s="1">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="J70" s="3" t="str">
         <f>IF(C70=H70,"Match","Different")</f>
@@ -7667,11 +7677,11 @@
       <c r="G71" s="6">
         <v>258</v>
       </c>
-      <c r="H71" s="22" t="s">
+      <c r="H71" s="24" t="s">
         <v>65</v>
       </c>
       <c r="I71" s="2">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J71" s="3" t="str">
         <f>IF(C71=H71,"Match","Different")</f>
@@ -7700,7 +7710,7 @@
       <c r="G72" s="6">
         <v>899</v>
       </c>
-      <c r="H72" s="22" t="s">
+      <c r="H72" s="23" t="s">
         <v>68</v>
       </c>
       <c r="I72" s="1">
@@ -7733,7 +7743,7 @@
       <c r="G73" s="6">
         <v>7372</v>
       </c>
-      <c r="H73" s="22" t="s">
+      <c r="H73" s="24" t="s">
         <v>61</v>
       </c>
       <c r="I73" s="2">
@@ -7766,7 +7776,7 @@
       <c r="G74" s="6">
         <v>325</v>
       </c>
-      <c r="H74" s="22" t="s">
+      <c r="H74" s="23" t="s">
         <v>71</v>
       </c>
       <c r="I74" s="1">
@@ -7799,7 +7809,7 @@
       <c r="G75" s="6">
         <v>2665</v>
       </c>
-      <c r="H75" s="22" t="s">
+      <c r="H75" s="24" t="s">
         <v>72</v>
       </c>
       <c r="I75" s="2">
@@ -7832,7 +7842,7 @@
       <c r="G76" s="6">
         <v>745</v>
       </c>
-      <c r="H76" s="22" t="s">
+      <c r="H76" s="23" t="s">
         <v>73</v>
       </c>
       <c r="I76" s="1">
@@ -7865,7 +7875,7 @@
       <c r="G77" s="6">
         <v>4700</v>
       </c>
-      <c r="H77" s="22" t="s">
+      <c r="H77" s="24" t="s">
         <v>74</v>
       </c>
       <c r="I77" s="2">
@@ -7898,7 +7908,7 @@
       <c r="G78" s="6">
         <v>1514</v>
       </c>
-      <c r="H78" s="22" t="s">
+      <c r="H78" s="23" t="s">
         <v>75</v>
       </c>
       <c r="I78" s="1">
@@ -7931,7 +7941,7 @@
       <c r="G79" s="6">
         <v>1191</v>
       </c>
-      <c r="H79" s="22" t="s">
+      <c r="H79" s="24" t="s">
         <v>76</v>
       </c>
       <c r="I79" s="2">
@@ -7964,11 +7974,11 @@
       <c r="G80" s="6">
         <v>32</v>
       </c>
-      <c r="H80" s="22" t="s">
+      <c r="H80" s="23" t="s">
         <v>77</v>
       </c>
       <c r="I80" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J80" s="3" t="str">
         <f>IF(C80=H80,"Match","Different")</f>
@@ -7997,7 +8007,7 @@
       <c r="G81" s="6">
         <v>3363</v>
       </c>
-      <c r="H81" s="22" t="s">
+      <c r="H81" s="24" t="s">
         <v>78</v>
       </c>
       <c r="I81" s="2">
@@ -8030,11 +8040,11 @@
       <c r="G82" s="6">
         <v>988</v>
       </c>
-      <c r="H82" s="22" t="s">
+      <c r="H82" s="23" t="s">
         <v>79</v>
       </c>
       <c r="I82" s="1">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J82" s="3" t="str">
         <f>IF(C82=H82,"Match","Different")</f>
@@ -8063,7 +8073,7 @@
       <c r="G83" s="6">
         <v>2448</v>
       </c>
-      <c r="H83" s="22" t="s">
+      <c r="H83" s="24" t="s">
         <v>80</v>
       </c>
       <c r="I83" s="2">
@@ -8096,11 +8106,11 @@
       <c r="G84" s="6">
         <v>139</v>
       </c>
-      <c r="H84" s="22" t="s">
+      <c r="H84" s="23" t="s">
         <v>81</v>
       </c>
       <c r="I84" s="1">
-        <v>6</v>
+        <v>31</v>
       </c>
       <c r="J84" s="3" t="str">
         <f>IF(C84=H84,"Match","Different")</f>
@@ -8129,7 +8139,7 @@
       <c r="G85" s="6">
         <v>1652</v>
       </c>
-      <c r="H85" s="22" t="s">
+      <c r="H85" s="24" t="s">
         <v>82</v>
       </c>
       <c r="I85" s="2">
@@ -8162,11 +8172,11 @@
       <c r="G86" s="6">
         <v>618</v>
       </c>
-      <c r="H86" s="22" t="s">
+      <c r="H86" s="23" t="s">
         <v>83</v>
       </c>
       <c r="I86" s="1">
-        <v>19</v>
+        <v>39</v>
       </c>
       <c r="J86" s="3" t="str">
         <f>IF(C86=H86,"Match","Different")</f>
@@ -8195,11 +8205,11 @@
       <c r="G87" s="6">
         <v>3453</v>
       </c>
-      <c r="H87" s="22" t="s">
+      <c r="H87" s="24" t="s">
         <v>84</v>
       </c>
       <c r="I87" s="2">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="J87" s="3" t="str">
         <f>IF(C87=H87,"Match","Different")</f>
@@ -8228,11 +8238,11 @@
       <c r="G88" s="12">
         <v>1515</v>
       </c>
-      <c r="H88" s="22" t="s">
+      <c r="H88" s="23" t="s">
         <v>85</v>
       </c>
       <c r="I88" s="1">
-        <v>173</v>
+        <v>204</v>
       </c>
       <c r="J88" s="3" t="str">
         <f>IF(C88=H88,"Match","Different")</f>
@@ -8261,7 +8271,7 @@
       <c r="G89" s="6">
         <v>371</v>
       </c>
-      <c r="H89" s="22" t="s">
+      <c r="H89" s="24" t="s">
         <v>86</v>
       </c>
       <c r="I89" s="2">
@@ -8294,11 +8304,11 @@
       <c r="G90" s="6">
         <v>2131</v>
       </c>
-      <c r="H90" s="22" t="s">
+      <c r="H90" s="23" t="s">
         <v>87</v>
       </c>
       <c r="I90" s="1">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="J90" s="3" t="str">
         <f>IF(C90=H90,"Match","Different")</f>
@@ -8327,11 +8337,11 @@
       <c r="G91" s="6">
         <v>1369</v>
       </c>
-      <c r="H91" s="22" t="s">
+      <c r="H91" s="24" t="s">
         <v>88</v>
       </c>
       <c r="I91" s="2">
-        <v>40</v>
+        <v>58</v>
       </c>
       <c r="J91" s="3" t="str">
         <f>IF(C91=H91,"Match","Different")</f>
@@ -8349,7 +8359,7 @@
         <v>89</v>
       </c>
       <c r="D92" s="8" t="s">
-        <v>195</v>
+        <v>184</v>
       </c>
       <c r="E92" s="9" t="s">
         <v>176</v>
@@ -8360,11 +8370,11 @@
       <c r="G92" s="6">
         <v>531</v>
       </c>
-      <c r="H92" s="22" t="s">
+      <c r="H92" s="23" t="s">
         <v>89</v>
       </c>
       <c r="I92" s="1">
-        <v>61</v>
+        <v>101</v>
       </c>
       <c r="J92" s="3" t="str">
         <f>IF(C92=H92,"Match","Different")</f>
@@ -8393,11 +8403,11 @@
       <c r="G93" s="6">
         <v>2029</v>
       </c>
-      <c r="H93" s="22" t="s">
+      <c r="H93" s="24" t="s">
         <v>90</v>
       </c>
       <c r="I93" s="2">
-        <v>28</v>
+        <v>55</v>
       </c>
       <c r="J93" s="3" t="str">
         <f>IF(C93=H93,"Match","Different")</f>
@@ -8426,11 +8436,11 @@
       <c r="G94" s="6">
         <v>204</v>
       </c>
-      <c r="H94" s="22" t="s">
+      <c r="H94" s="23" t="s">
         <v>91</v>
       </c>
       <c r="I94" s="1">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="J94" s="3" t="str">
         <f>IF(C94=H94,"Match","Different")</f>
@@ -8459,7 +8469,7 @@
       <c r="G95" s="6">
         <v>230</v>
       </c>
-      <c r="H95" s="22" t="s">
+      <c r="H95" s="24" t="s">
         <v>92</v>
       </c>
       <c r="I95" s="2">
@@ -8492,11 +8502,11 @@
       <c r="G96" s="6">
         <v>1109</v>
       </c>
-      <c r="H96" s="22" t="s">
+      <c r="H96" s="23" t="s">
         <v>93</v>
       </c>
       <c r="I96" s="1">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="J96" s="3" t="str">
         <f>IF(C96=H96,"Match","Different")</f>
@@ -8525,11 +8535,11 @@
       <c r="G97" s="6">
         <v>1145</v>
       </c>
-      <c r="H97" s="22" t="s">
+      <c r="H97" s="24" t="s">
         <v>94</v>
       </c>
       <c r="I97" s="2">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="J97" s="3" t="str">
         <f>IF(C97=H97,"Match","Different")</f>
@@ -8558,7 +8568,7 @@
       <c r="G98" s="6">
         <v>2506</v>
       </c>
-      <c r="H98" s="22" t="s">
+      <c r="H98" s="23" t="s">
         <v>95</v>
       </c>
       <c r="I98" s="1">
@@ -8580,7 +8590,7 @@
         <v>96</v>
       </c>
       <c r="D99" s="8" t="s">
-        <v>195</v>
+        <v>184</v>
       </c>
       <c r="E99" s="9" t="s">
         <v>176</v>
@@ -8591,11 +8601,11 @@
       <c r="G99" s="6">
         <v>2345</v>
       </c>
-      <c r="H99" s="22" t="s">
+      <c r="H99" s="24" t="s">
         <v>96</v>
       </c>
       <c r="I99" s="2">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="J99" s="3" t="str">
         <f>IF(C99=H99,"Match","Different")</f>
@@ -8624,11 +8634,11 @@
       <c r="G100" s="6">
         <v>6268</v>
       </c>
-      <c r="H100" s="22" t="s">
+      <c r="H100" s="23" t="s">
         <v>97</v>
       </c>
       <c r="I100" s="1">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="J100" s="3" t="str">
         <f>IF(C100=H100,"Match","Different")</f>
@@ -8657,11 +8667,11 @@
       <c r="G101" s="6">
         <v>2855</v>
       </c>
-      <c r="H101" s="22" t="s">
+      <c r="H101" s="24" t="s">
         <v>98</v>
       </c>
       <c r="I101" s="2">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="J101" s="3" t="str">
         <f>IF(C101=H101,"Match","Different")</f>
@@ -8690,11 +8700,11 @@
       <c r="G102" s="6">
         <v>676</v>
       </c>
-      <c r="H102" s="22" t="s">
+      <c r="H102" s="23" t="s">
         <v>99</v>
       </c>
       <c r="I102" s="1">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="J102" s="3" t="str">
         <f>IF(C102=H102,"Match","Different")</f>
@@ -8723,11 +8733,11 @@
       <c r="G103" s="6">
         <v>658</v>
       </c>
-      <c r="H103" s="22" t="s">
+      <c r="H103" s="24" t="s">
         <v>100</v>
       </c>
       <c r="I103" s="2">
-        <v>5</v>
+        <v>28</v>
       </c>
       <c r="J103" s="3" t="str">
         <f>IF(C103=H103,"Match","Different")</f>
@@ -8756,11 +8766,11 @@
       <c r="G104" s="6">
         <v>980</v>
       </c>
-      <c r="H104" s="22" t="s">
+      <c r="H104" s="23" t="s">
         <v>101</v>
       </c>
       <c r="I104" s="1">
-        <v>14</v>
+        <v>62</v>
       </c>
       <c r="J104" s="3" t="str">
         <f>IF(C104=H104,"Match","Different")</f>
@@ -8789,7 +8799,7 @@
       <c r="G105" s="6">
         <v>1948</v>
       </c>
-      <c r="H105" s="22" t="s">
+      <c r="H105" s="24" t="s">
         <v>102</v>
       </c>
       <c r="I105" s="2">
@@ -8822,7 +8832,7 @@
       <c r="G106" s="6">
         <v>899</v>
       </c>
-      <c r="H106" s="22" t="s">
+      <c r="H106" s="23" t="s">
         <v>103</v>
       </c>
       <c r="I106" s="1">
@@ -8855,11 +8865,11 @@
       <c r="G107" s="6">
         <v>402</v>
       </c>
-      <c r="H107" s="22" t="s">
+      <c r="H107" s="24" t="s">
         <v>104</v>
       </c>
       <c r="I107" s="2">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="J107" s="3" t="str">
         <f>IF(C107=H107,"Match","Different")</f>
@@ -8888,7 +8898,7 @@
       <c r="G108" s="6">
         <v>286</v>
       </c>
-      <c r="H108" s="22" t="s">
+      <c r="H108" s="23" t="s">
         <v>105</v>
       </c>
       <c r="I108" s="1">
@@ -8921,7 +8931,7 @@
       <c r="G109" s="6">
         <v>737</v>
       </c>
-      <c r="H109" s="22" t="s">
+      <c r="H109" s="24" t="s">
         <v>106</v>
       </c>
       <c r="I109" s="2">
@@ -8943,7 +8953,7 @@
         <v>107</v>
       </c>
       <c r="D110" s="5" t="s">
-        <v>161</v>
+        <v>151</v>
       </c>
       <c r="E110" s="5" t="s">
         <v>133</v>
@@ -8954,7 +8964,7 @@
       <c r="G110" s="6">
         <v>429</v>
       </c>
-      <c r="H110" s="22" t="s">
+      <c r="H110" s="23" t="s">
         <v>107</v>
       </c>
       <c r="I110" s="1">
@@ -8976,7 +8986,7 @@
         <v>108</v>
       </c>
       <c r="D111" s="5" t="s">
-        <v>151</v>
+        <v>161</v>
       </c>
       <c r="E111" s="5" t="s">
         <v>133</v>
@@ -8987,7 +8997,7 @@
       <c r="G111" s="6">
         <v>822</v>
       </c>
-      <c r="H111" s="22" t="s">
+      <c r="H111" s="24" t="s">
         <v>108</v>
       </c>
       <c r="I111" s="2">
@@ -9020,7 +9030,7 @@
       <c r="G112" s="6">
         <v>646</v>
       </c>
-      <c r="H112" s="22" t="s">
+      <c r="H112" s="23" t="s">
         <v>109</v>
       </c>
       <c r="I112" s="1">
@@ -9053,7 +9063,7 @@
       <c r="G113" s="6">
         <v>302</v>
       </c>
-      <c r="H113" s="22" t="s">
+      <c r="H113" s="24" t="s">
         <v>110</v>
       </c>
       <c r="I113" s="2">
@@ -9086,7 +9096,7 @@
       <c r="G114" s="6">
         <v>798</v>
       </c>
-      <c r="H114" s="22" t="s">
+      <c r="H114" s="23" t="s">
         <v>111</v>
       </c>
       <c r="I114" s="1">
@@ -9119,7 +9129,7 @@
       <c r="G115" s="6">
         <v>222</v>
       </c>
-      <c r="H115" s="22" t="s">
+      <c r="H115" s="24" t="s">
         <v>112</v>
       </c>
       <c r="I115" s="2">
@@ -9152,7 +9162,7 @@
       <c r="G116" s="6">
         <v>362</v>
       </c>
-      <c r="H116" s="22" t="s">
+      <c r="H116" s="23" t="s">
         <v>113</v>
       </c>
       <c r="I116" s="1">
@@ -9185,7 +9195,7 @@
       <c r="G117" s="6">
         <v>769</v>
       </c>
-      <c r="H117" s="22" t="s">
+      <c r="H117" s="24" t="s">
         <v>114</v>
       </c>
       <c r="I117" s="2">
@@ -9218,7 +9228,7 @@
       <c r="G118" s="6">
         <v>325</v>
       </c>
-      <c r="H118" s="22" t="s">
+      <c r="H118" s="23" t="s">
         <v>115</v>
       </c>
       <c r="I118" s="1">
@@ -9251,11 +9261,11 @@
       <c r="G119" s="6">
         <v>421</v>
       </c>
-      <c r="H119" s="22" t="s">
+      <c r="H119" s="24" t="s">
         <v>7</v>
       </c>
       <c r="I119" s="2">
-        <v>17</v>
+        <v>37</v>
       </c>
       <c r="J119" s="3" t="str">
         <f>IF(C119=H119,"Match","Different")</f>
@@ -9284,11 +9294,11 @@
       <c r="G120" s="17">
         <v>281</v>
       </c>
-      <c r="H120" s="22" t="s">
+      <c r="H120" s="23" t="s">
         <v>116</v>
       </c>
       <c r="I120" s="1">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="J120" s="3" t="str">
         <f>IF(C120=H120,"Match","Different")</f>
@@ -9317,7 +9327,7 @@
       <c r="G121" s="6">
         <v>517</v>
       </c>
-      <c r="H121" s="22" t="s">
+      <c r="H121" s="24" t="s">
         <v>117</v>
       </c>
       <c r="I121" s="2">
@@ -9350,7 +9360,7 @@
       <c r="G122" s="6">
         <v>166</v>
       </c>
-      <c r="H122" s="22" t="s">
+      <c r="H122" s="23" t="s">
         <v>118</v>
       </c>
       <c r="I122" s="1">
@@ -9383,11 +9393,11 @@
       <c r="G123" s="6">
         <v>633</v>
       </c>
-      <c r="H123" s="22" t="s">
+      <c r="H123" s="24" t="s">
         <v>119</v>
       </c>
       <c r="I123" s="2">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="J123" s="3" t="str">
         <f>IF(C123=H123,"Match","Different")</f>
@@ -9416,7 +9426,7 @@
       <c r="G124" s="6">
         <v>128</v>
       </c>
-      <c r="H124" s="22" t="s">
+      <c r="H124" s="23" t="s">
         <v>120</v>
       </c>
       <c r="I124" s="1">
@@ -9449,7 +9459,7 @@
       <c r="G125" s="6">
         <v>192</v>
       </c>
-      <c r="H125" s="22" t="s">
+      <c r="H125" s="24" t="s">
         <v>121</v>
       </c>
       <c r="I125" s="2">
